--- a/data/trans_bre/P19C02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C02-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 9,63</t>
+          <t>-2,95; 9,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 9,59</t>
+          <t>-3,81; 9,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 7,65</t>
+          <t>-6,31; 7,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 5,36</t>
+          <t>-18,93; 5,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 44,7</t>
+          <t>-10,51; 45,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 46,96</t>
+          <t>-14,56; 44,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 26,26</t>
+          <t>-17,83; 24,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 14,74</t>
+          <t>-36,01; 15,49</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 5,23</t>
+          <t>-6,98; 4,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 5,63</t>
+          <t>-5,97; 5,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 3,56</t>
+          <t>-8,6; 3,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,42; 0,86</t>
+          <t>-28,68; 1,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 13,87</t>
+          <t>-16,97; 14,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 16,98</t>
+          <t>-15,4; 17,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 9,5</t>
+          <t>-20,01; 9,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,82; 1,4</t>
+          <t>-47,41; 3,4</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 3,84</t>
+          <t>-7,84; 4,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 6,02</t>
+          <t>-4,91; 6,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 8,16</t>
+          <t>-3,62; 7,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 6,07</t>
+          <t>-4,92; 6,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 11,62</t>
+          <t>-20,28; 11,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 17,21</t>
+          <t>-11,9; 17,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 20,6</t>
+          <t>-7,68; 20,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 11,44</t>
+          <t>-8,33; 11,51</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 7,29</t>
+          <t>-5,3; 7,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 11,15</t>
+          <t>-1,3; 10,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 12,81</t>
+          <t>0,41; 13,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 38,5</t>
+          <t>-1,12; 36,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 26,09</t>
+          <t>-15,46; 25,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 36,52</t>
+          <t>-3,78; 35,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 37,98</t>
+          <t>0,8; 38,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 211,66</t>
+          <t>-2,11; 208,92</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 12,27</t>
+          <t>-1,16; 11,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 11,74</t>
+          <t>-1,84; 12,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 13,52</t>
+          <t>-0,41; 13,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 10,66</t>
+          <t>0,45; 10,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 77,29</t>
+          <t>-5,37; 72,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 58,85</t>
+          <t>-6,66; 61,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 55,75</t>
+          <t>-1,21; 57,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 25,08</t>
+          <t>0,89; 24,66</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 14,3</t>
+          <t>1,46; 13,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 11,14</t>
+          <t>-2,18; 11,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 15,61</t>
+          <t>0,93; 16,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,36; 48,7</t>
+          <t>2,64; 47,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 211,26</t>
+          <t>10,71; 192,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 113,74</t>
+          <t>-12,91; 109,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 88,4</t>
+          <t>3,5; 92,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 136,46</t>
+          <t>6,61; 130,61</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,59</t>
+          <t>-4,63; 5,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 3,13</t>
+          <t>-10,02; 2,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 8,3</t>
+          <t>-8,3; 8,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 8,16</t>
+          <t>-2,26; 8,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,84; 190,09</t>
+          <t>-66,01; 249,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 27,98</t>
+          <t>-54,08; 27,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 55,1</t>
+          <t>-35,49; 61,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 36,84</t>
+          <t>-8,29; 37,24</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,19</t>
+          <t>-2,11; 2,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,1</t>
+          <t>-0,71; 4,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,01</t>
+          <t>-0,38; 5,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 18,45</t>
+          <t>-0,12; 19,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 11,65</t>
+          <t>-6,98; 10,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 14,36</t>
+          <t>-2,39; 14,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 14,8</t>
+          <t>-1,22; 15,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 48,32</t>
+          <t>-0,21; 50,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C02-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,33</t>
+          <t>-2,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-14,11%</t>
+          <t>-6,24%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 9,91</t>
+          <t>-3,5; 9,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 9,18</t>
+          <t>-3,65; 9,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 7,26</t>
+          <t>-6,68; 7,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 5,44</t>
+          <t>-14,5; 8,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 45,66</t>
+          <t>-12,43; 40,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 44,33</t>
+          <t>-13,52; 45,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 24,37</t>
+          <t>-18,1; 24,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 15,49</t>
+          <t>-27,8; 20,93</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-8,81</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-15,92%</t>
+          <t>-3,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 4,98</t>
+          <t>-6,53; 5,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 5,92</t>
+          <t>-5,83; 6,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 3,6</t>
+          <t>-8,61; 3,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 1,92</t>
+          <t>-9,53; 5,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 14,02</t>
+          <t>-15,7; 15,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 17,98</t>
+          <t>-15,03; 19,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 9,5</t>
+          <t>-19,8; 10,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,41; 3,4</t>
+          <t>-15,96; 11,19</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 4,02</t>
+          <t>-7,89; 3,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 6,3</t>
+          <t>-4,42; 6,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 7,88</t>
+          <t>-3,52; 8,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 6,16</t>
+          <t>-4,11; 7,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 11,98</t>
+          <t>-20,59; 10,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 17,98</t>
+          <t>-10,74; 20,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 20,51</t>
+          <t>-7,73; 21,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 11,51</t>
+          <t>-6,93; 13,5</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,79</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 7,06</t>
+          <t>-4,95; 7,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 10,98</t>
+          <t>-1,59; 10,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 13,09</t>
+          <t>0,22; 12,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 36,93</t>
+          <t>-0,39; 9,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 25,69</t>
+          <t>-14,47; 28,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 35,88</t>
+          <t>-4,47; 35,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 38,97</t>
+          <t>0,52; 37,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 208,92</t>
+          <t>-0,69; 20,67</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,66</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 11,7</t>
+          <t>-0,81; 12,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 12,18</t>
+          <t>-1,44; 12,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 13,96</t>
+          <t>-0,3; 13,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 10,48</t>
+          <t>0,4; 10,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 72,81</t>
+          <t>-6,01; 76,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 61,79</t>
+          <t>-5,44; 59,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 57,57</t>
+          <t>-0,91; 55,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 24,66</t>
+          <t>0,79; 23,69</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23,42</t>
+          <t>3,27</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,59</t>
+          <t>1,55; 13,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 11,28</t>
+          <t>-1,85; 10,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 16,64</t>
+          <t>0,17; 15,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 47,29</t>
+          <t>-2,01; 8,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 192,31</t>
+          <t>11,2; 201,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 109,57</t>
+          <t>-10,19; 113,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 92,99</t>
+          <t>1,15; 87,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 130,61</t>
+          <t>-4,67; 21,77</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 5,34</t>
+          <t>-5,56; 4,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 2,82</t>
+          <t>-9,88; 3,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 8,71</t>
+          <t>-7,57; 8,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 8,23</t>
+          <t>-2,09; 9,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 249,82</t>
+          <t>-70,48; 206,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-54,08; 27,64</t>
+          <t>-49,71; 39,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 61,56</t>
+          <t>-33,45; 59,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 37,24</t>
+          <t>-7,42; 39,13</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,9</t>
+          <t>-1,9; 3,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,14</t>
+          <t>-0,86; 4,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,15</t>
+          <t>-0,25; 5,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 19,1</t>
+          <t>-0,95; 3,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 10,64</t>
+          <t>-6,44; 11,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 14,47</t>
+          <t>-2,69; 14,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 15,31</t>
+          <t>-0,69; 15,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 50,78</t>
+          <t>-1,94; 8,52</t>
         </is>
       </c>
     </row>
